--- a/artfynd/A 54102-2023 artfynd.xlsx
+++ b/artfynd/A 54102-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121466192</v>
+        <v>121466194</v>
       </c>
       <c r="B2" t="n">
-        <v>74700</v>
+        <v>74702</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409611</v>
+        <v>409565</v>
       </c>
       <c r="R2" t="n">
-        <v>6348255</v>
+        <v>6348183</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sparsamt</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121466183</v>
+        <v>121466193</v>
       </c>
       <c r="B3" t="n">
-        <v>91380</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409609</v>
+        <v>409585</v>
       </c>
       <c r="R3" t="n">
-        <v>6348291</v>
+        <v>6348172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121466194</v>
+        <v>121466196</v>
       </c>
       <c r="B4" t="n">
-        <v>74700</v>
+        <v>74702</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409565</v>
+        <v>409589</v>
       </c>
       <c r="R4" t="n">
-        <v>6348183</v>
+        <v>6348121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,7 +989,7 @@
         <v>121466197</v>
       </c>
       <c r="B5" t="n">
-        <v>74700</v>
+        <v>74702</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121466193</v>
+        <v>121466192</v>
       </c>
       <c r="B6" t="n">
-        <v>57367</v>
+        <v>74702</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409585</v>
+        <v>409611</v>
       </c>
       <c r="R6" t="n">
-        <v>6348172</v>
+        <v>6348255</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121466196</v>
+        <v>121466183</v>
       </c>
       <c r="B7" t="n">
-        <v>74700</v>
+        <v>91392</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409589</v>
+        <v>409609</v>
       </c>
       <c r="R7" t="n">
-        <v>6348121</v>
+        <v>6348291</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 54102-2023 artfynd.xlsx
+++ b/artfynd/A 54102-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121466194</v>
+        <v>121466196</v>
       </c>
       <c r="B2" t="n">
         <v>74702</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409565</v>
+        <v>409589</v>
       </c>
       <c r="R2" t="n">
-        <v>6348183</v>
+        <v>6348121</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121466193</v>
+        <v>121466194</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>74702</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409585</v>
+        <v>409565</v>
       </c>
       <c r="R3" t="n">
-        <v>6348172</v>
+        <v>6348183</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121466196</v>
+        <v>121466197</v>
       </c>
       <c r="B4" t="n">
         <v>74702</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409589</v>
+        <v>409624</v>
       </c>
       <c r="R4" t="n">
-        <v>6348121</v>
+        <v>6348034</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121466197</v>
+        <v>121466193</v>
       </c>
       <c r="B5" t="n">
-        <v>74702</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409624</v>
+        <v>409585</v>
       </c>
       <c r="R5" t="n">
-        <v>6348034</v>
+        <v>6348172</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121466192</v>
+        <v>121466183</v>
       </c>
       <c r="B6" t="n">
-        <v>74702</v>
+        <v>91393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409611</v>
+        <v>409609</v>
       </c>
       <c r="R6" t="n">
-        <v>6348255</v>
+        <v>6348291</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121466183</v>
+        <v>121466192</v>
       </c>
       <c r="B7" t="n">
-        <v>91392</v>
+        <v>74702</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409609</v>
+        <v>409611</v>
       </c>
       <c r="R7" t="n">
-        <v>6348291</v>
+        <v>6348255</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54102-2023 artfynd.xlsx
+++ b/artfynd/A 54102-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121466196</v>
+        <v>121466194</v>
       </c>
       <c r="B2" t="n">
-        <v>74702</v>
+        <v>74705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409589</v>
+        <v>409565</v>
       </c>
       <c r="R2" t="n">
-        <v>6348121</v>
+        <v>6348183</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121466194</v>
+        <v>121466197</v>
       </c>
       <c r="B3" t="n">
-        <v>74702</v>
+        <v>74705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409565</v>
+        <v>409624</v>
       </c>
       <c r="R3" t="n">
-        <v>6348183</v>
+        <v>6348034</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121466197</v>
+        <v>121466196</v>
       </c>
       <c r="B4" t="n">
-        <v>74702</v>
+        <v>74705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409624</v>
+        <v>409589</v>
       </c>
       <c r="R4" t="n">
-        <v>6348034</v>
+        <v>6348121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121466193</v>
+        <v>121466183</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>91396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409585</v>
+        <v>409609</v>
       </c>
       <c r="R5" t="n">
-        <v>6348172</v>
+        <v>6348291</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121466183</v>
+        <v>121466192</v>
       </c>
       <c r="B6" t="n">
-        <v>91393</v>
+        <v>74705</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409609</v>
+        <v>409611</v>
       </c>
       <c r="R6" t="n">
-        <v>6348291</v>
+        <v>6348255</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121466192</v>
+        <v>121466193</v>
       </c>
       <c r="B7" t="n">
-        <v>74702</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409611</v>
+        <v>409585</v>
       </c>
       <c r="R7" t="n">
-        <v>6348255</v>
+        <v>6348172</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54102-2023 artfynd.xlsx
+++ b/artfynd/A 54102-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121466194</v>
+        <v>121466193</v>
       </c>
       <c r="B2" t="n">
-        <v>74705</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409565</v>
+        <v>409585</v>
       </c>
       <c r="R2" t="n">
-        <v>6348183</v>
+        <v>6348172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121466197</v>
+        <v>121466192</v>
       </c>
       <c r="B3" t="n">
         <v>74705</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409624</v>
+        <v>409611</v>
       </c>
       <c r="R3" t="n">
-        <v>6348034</v>
+        <v>6348255</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sparsamt</t>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121466183</v>
+        <v>121466197</v>
       </c>
       <c r="B5" t="n">
-        <v>91396</v>
+        <v>74705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409609</v>
+        <v>409624</v>
       </c>
       <c r="R5" t="n">
-        <v>6348291</v>
+        <v>6348034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121466192</v>
+        <v>121466183</v>
       </c>
       <c r="B6" t="n">
-        <v>74705</v>
+        <v>91396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409611</v>
+        <v>409609</v>
       </c>
       <c r="R6" t="n">
-        <v>6348255</v>
+        <v>6348291</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121466193</v>
+        <v>121466194</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>74705</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409585</v>
+        <v>409565</v>
       </c>
       <c r="R7" t="n">
-        <v>6348172</v>
+        <v>6348183</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54102-2023 artfynd.xlsx
+++ b/artfynd/A 54102-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121466193</v>
+        <v>121466196</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>74706</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409585</v>
+        <v>409589</v>
       </c>
       <c r="R2" t="n">
-        <v>6348172</v>
+        <v>6348121</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121466192</v>
+        <v>121466194</v>
       </c>
       <c r="B3" t="n">
-        <v>74705</v>
+        <v>74706</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409611</v>
+        <v>409565</v>
       </c>
       <c r="R3" t="n">
-        <v>6348255</v>
+        <v>6348183</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sparsamt</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121466196</v>
+        <v>121466193</v>
       </c>
       <c r="B4" t="n">
-        <v>74705</v>
+        <v>57371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409589</v>
+        <v>409585</v>
       </c>
       <c r="R4" t="n">
-        <v>6348121</v>
+        <v>6348172</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121466197</v>
+        <v>121466183</v>
       </c>
       <c r="B5" t="n">
-        <v>74705</v>
+        <v>91402</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409624</v>
+        <v>409609</v>
       </c>
       <c r="R5" t="n">
-        <v>6348034</v>
+        <v>6348291</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121466183</v>
+        <v>121466197</v>
       </c>
       <c r="B6" t="n">
-        <v>91396</v>
+        <v>74706</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409609</v>
+        <v>409624</v>
       </c>
       <c r="R6" t="n">
-        <v>6348291</v>
+        <v>6348034</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121466194</v>
+        <v>121466192</v>
       </c>
       <c r="B7" t="n">
-        <v>74705</v>
+        <v>74706</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409565</v>
+        <v>409611</v>
       </c>
       <c r="R7" t="n">
-        <v>6348183</v>
+        <v>6348255</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54102-2023 artfynd.xlsx
+++ b/artfynd/A 54102-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121466196</v>
+        <v>121466194</v>
       </c>
       <c r="B2" t="n">
-        <v>74706</v>
+        <v>74707</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409589</v>
+        <v>409565</v>
       </c>
       <c r="R2" t="n">
-        <v>6348121</v>
+        <v>6348183</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121466194</v>
+        <v>121466183</v>
       </c>
       <c r="B3" t="n">
-        <v>74706</v>
+        <v>91403</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409565</v>
+        <v>409609</v>
       </c>
       <c r="R3" t="n">
-        <v>6348183</v>
+        <v>6348291</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121466193</v>
+        <v>121466196</v>
       </c>
       <c r="B4" t="n">
-        <v>57371</v>
+        <v>74707</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409585</v>
+        <v>409589</v>
       </c>
       <c r="R4" t="n">
-        <v>6348172</v>
+        <v>6348121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121466183</v>
+        <v>121466192</v>
       </c>
       <c r="B5" t="n">
-        <v>91402</v>
+        <v>74707</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409609</v>
+        <v>409611</v>
       </c>
       <c r="R5" t="n">
-        <v>6348291</v>
+        <v>6348255</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,7 +1096,7 @@
         <v>121466197</v>
       </c>
       <c r="B6" t="n">
-        <v>74706</v>
+        <v>74707</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121466192</v>
+        <v>121466193</v>
       </c>
       <c r="B7" t="n">
-        <v>74706</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409611</v>
+        <v>409585</v>
       </c>
       <c r="R7" t="n">
-        <v>6348255</v>
+        <v>6348172</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54102-2023 artfynd.xlsx
+++ b/artfynd/A 54102-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121466183</v>
+        <v>121466193</v>
       </c>
       <c r="B3" t="n">
-        <v>91403</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409609</v>
+        <v>409585</v>
       </c>
       <c r="R3" t="n">
-        <v>6348291</v>
+        <v>6348172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121466193</v>
+        <v>121466183</v>
       </c>
       <c r="B7" t="n">
-        <v>57372</v>
+        <v>91403</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409585</v>
+        <v>409609</v>
       </c>
       <c r="R7" t="n">
-        <v>6348172</v>
+        <v>6348291</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 54102-2023 artfynd.xlsx
+++ b/artfynd/A 54102-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121466194</v>
+        <v>121466183</v>
       </c>
       <c r="B2" t="n">
-        <v>74707</v>
+        <v>91403</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409565</v>
+        <v>409609</v>
       </c>
       <c r="R2" t="n">
-        <v>6348183</v>
+        <v>6348291</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121466193</v>
+        <v>121466194</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>74707</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409585</v>
+        <v>409565</v>
       </c>
       <c r="R3" t="n">
-        <v>6348172</v>
+        <v>6348183</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121466196</v>
+        <v>121466192</v>
       </c>
       <c r="B4" t="n">
         <v>74707</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409589</v>
+        <v>409611</v>
       </c>
       <c r="R4" t="n">
-        <v>6348121</v>
+        <v>6348255</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121466192</v>
+        <v>121466193</v>
       </c>
       <c r="B5" t="n">
-        <v>74707</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409611</v>
+        <v>409585</v>
       </c>
       <c r="R5" t="n">
-        <v>6348255</v>
+        <v>6348172</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121466197</v>
+        <v>121466196</v>
       </c>
       <c r="B6" t="n">
         <v>74707</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409624</v>
+        <v>409589</v>
       </c>
       <c r="R6" t="n">
-        <v>6348034</v>
+        <v>6348121</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121466183</v>
+        <v>121466197</v>
       </c>
       <c r="B7" t="n">
-        <v>91403</v>
+        <v>74707</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409609</v>
+        <v>409624</v>
       </c>
       <c r="R7" t="n">
-        <v>6348291</v>
+        <v>6348034</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54102-2023 artfynd.xlsx
+++ b/artfynd/A 54102-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121466183</v>
+        <v>121466193</v>
       </c>
       <c r="B2" t="n">
-        <v>91403</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409609</v>
+        <v>409585</v>
       </c>
       <c r="R2" t="n">
-        <v>6348291</v>
+        <v>6348172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121466194</v>
+        <v>121466183</v>
       </c>
       <c r="B3" t="n">
-        <v>74707</v>
+        <v>91403</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409565</v>
+        <v>409609</v>
       </c>
       <c r="R3" t="n">
-        <v>6348183</v>
+        <v>6348291</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121466192</v>
+        <v>121466196</v>
       </c>
       <c r="B4" t="n">
         <v>74707</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409611</v>
+        <v>409589</v>
       </c>
       <c r="R4" t="n">
-        <v>6348255</v>
+        <v>6348121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121466193</v>
+        <v>121466197</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>74707</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409585</v>
+        <v>409624</v>
       </c>
       <c r="R5" t="n">
-        <v>6348172</v>
+        <v>6348034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121466196</v>
+        <v>121466194</v>
       </c>
       <c r="B6" t="n">
         <v>74707</v>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409589</v>
+        <v>409565</v>
       </c>
       <c r="R6" t="n">
-        <v>6348121</v>
+        <v>6348183</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121466197</v>
+        <v>121466192</v>
       </c>
       <c r="B7" t="n">
         <v>74707</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409624</v>
+        <v>409611</v>
       </c>
       <c r="R7" t="n">
-        <v>6348034</v>
+        <v>6348255</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Sparsamt</t>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54102-2023 artfynd.xlsx
+++ b/artfynd/A 54102-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121466196</v>
+        <v>121466193</v>
       </c>
       <c r="B2" t="n">
-        <v>74714</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409589</v>
+        <v>409585</v>
       </c>
       <c r="R2" t="n">
-        <v>6348121</v>
+        <v>6348172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121466193</v>
+        <v>121466196</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>74714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409585</v>
+        <v>409589</v>
       </c>
       <c r="R3" t="n">
-        <v>6348172</v>
+        <v>6348121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121466192</v>
+        <v>121466183</v>
       </c>
       <c r="B5" t="n">
-        <v>74714</v>
+        <v>91411</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409611</v>
+        <v>409609</v>
       </c>
       <c r="R5" t="n">
-        <v>6348255</v>
+        <v>6348291</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121466183</v>
+        <v>121466192</v>
       </c>
       <c r="B6" t="n">
-        <v>91411</v>
+        <v>74714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409609</v>
+        <v>409611</v>
       </c>
       <c r="R6" t="n">
-        <v>6348291</v>
+        <v>6348255</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 54102-2023 artfynd.xlsx
+++ b/artfynd/A 54102-2023 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121466196</v>
+        <v>121466194</v>
       </c>
       <c r="B3" t="n">
         <v>74714</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409589</v>
+        <v>409565</v>
       </c>
       <c r="R3" t="n">
-        <v>6348121</v>
+        <v>6348183</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121466194</v>
+        <v>121466192</v>
       </c>
       <c r="B4" t="n">
         <v>74714</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409565</v>
+        <v>409611</v>
       </c>
       <c r="R4" t="n">
-        <v>6348183</v>
+        <v>6348255</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121466183</v>
+        <v>121466196</v>
       </c>
       <c r="B5" t="n">
-        <v>91411</v>
+        <v>74714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409609</v>
+        <v>409589</v>
       </c>
       <c r="R5" t="n">
-        <v>6348291</v>
+        <v>6348121</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121466192</v>
+        <v>121466197</v>
       </c>
       <c r="B6" t="n">
         <v>74714</v>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409611</v>
+        <v>409624</v>
       </c>
       <c r="R6" t="n">
-        <v>6348255</v>
+        <v>6348034</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sparsamt</t>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121466197</v>
+        <v>121466183</v>
       </c>
       <c r="B7" t="n">
-        <v>74714</v>
+        <v>91411</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409624</v>
+        <v>409609</v>
       </c>
       <c r="R7" t="n">
-        <v>6348034</v>
+        <v>6348291</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54102-2023 artfynd.xlsx
+++ b/artfynd/A 54102-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121466193</v>
+        <v>121466192</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409585</v>
+        <v>409611</v>
       </c>
       <c r="R2" t="n">
-        <v>6348172</v>
+        <v>6348255</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,12 +780,7 @@
         <v>121466194</v>
       </c>
       <c r="B3" t="n">
-        <v>74714</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121466192</v>
+        <v>121466196</v>
       </c>
       <c r="B4" t="n">
-        <v>74714</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409611</v>
+        <v>409589</v>
       </c>
       <c r="R4" t="n">
-        <v>6348255</v>
+        <v>6348121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121466196</v>
+        <v>121466197</v>
       </c>
       <c r="B5" t="n">
-        <v>74714</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409589</v>
+        <v>409624</v>
       </c>
       <c r="R5" t="n">
-        <v>6348121</v>
+        <v>6348034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,37 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121466197</v>
+        <v>121466183</v>
       </c>
       <c r="B6" t="n">
-        <v>74714</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409624</v>
+        <v>409609</v>
       </c>
       <c r="R6" t="n">
-        <v>6348034</v>
+        <v>6348291</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,15 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121466183</v>
+        <v>121466193</v>
       </c>
       <c r="B7" t="n">
-        <v>91411</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409609</v>
+        <v>409585</v>
       </c>
       <c r="R7" t="n">
-        <v>6348291</v>
+        <v>6348172</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 54102-2023 artfynd.xlsx
+++ b/artfynd/A 54102-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121466192</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121466194</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121466196</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121466197</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121466183</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,8 +1299,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121466193</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>